--- a/data/trans_dic/IP16A98-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 28,05</t>
+          <t>6,43; 27,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,71; 42,42</t>
+          <t>10,7; 40,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,41; 40,89</t>
+          <t>13,58; 41,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,67; 31,68</t>
+          <t>8,71; 31,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 37,42</t>
+          <t>7,06; 35,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,07; 45,38</t>
+          <t>9,12; 41,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 24,98</t>
+          <t>10,12; 25,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 32,93</t>
+          <t>12,66; 32,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,62; 36,05</t>
+          <t>13,55; 35,82</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,96; 30,07</t>
+          <t>9,65; 29,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,36; 35,42</t>
+          <t>13,98; 35,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,55; 52,18</t>
+          <t>8,93; 51,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 22,42</t>
+          <t>5,18; 23,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,91; 36,62</t>
+          <t>15,08; 36,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 23,73</t>
+          <t>9,14; 24,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,22; 22,02</t>
+          <t>9,98; 22,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,33; 32,26</t>
+          <t>16,83; 31,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,55; 33,83</t>
+          <t>11,43; 33,03</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 15,61</t>
+          <t>1,8; 15,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 18,3</t>
+          <t>1,91; 18,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,57; 25,02</t>
+          <t>3,79; 25,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 19,22</t>
+          <t>3,53; 19,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 31,4</t>
+          <t>8,47; 32,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,52; 35,42</t>
+          <t>7,33; 36,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 13,88</t>
+          <t>3,84; 15,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 21,17</t>
+          <t>6,5; 20,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,52; 25,34</t>
+          <t>7,49; 25,32</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 18,34</t>
+          <t>3,21; 16,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 25,02</t>
+          <t>4,15; 23,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,85; 29,62</t>
+          <t>7,42; 29,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 31,86</t>
+          <t>10,88; 31,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 31,05</t>
+          <t>7,47; 31,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,59; 38,79</t>
+          <t>13,45; 38,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 22,37</t>
+          <t>9,36; 21,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 23,72</t>
+          <t>8,07; 23,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,24; 29,16</t>
+          <t>13,36; 29,95</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 16,92</t>
+          <t>8,11; 16,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 22,82</t>
+          <t>12,32; 23,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,46; 27,41</t>
+          <t>11,06; 28,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,93; 20,32</t>
+          <t>10,71; 20,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,75; 26,83</t>
+          <t>14,86; 27,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,19; 25,16</t>
+          <t>13,53; 25,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,65; 17,31</t>
+          <t>10,81; 17,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,93; 22,79</t>
+          <t>14,85; 22,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,66; 24,32</t>
+          <t>13,02; 23,65</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4857</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5728</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6561</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5990</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4562</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10847</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>10290</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>12721</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2023; 8749</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2606; 9785</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3509; 10677</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2938; 10489</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1706; 8644</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2523; 11453</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6597; 16421</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>6145; 15853</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>7252; 19163</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7213</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9930</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10427</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4775</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>10180</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9596</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11988</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>20110</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>20023</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3776; 11366</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5968; 15016</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3952; 22692</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2089; 9353</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>6204; 15046</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5832; 15874</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7926; 17967</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>14114; 26777</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>12352; 35692</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1881</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10778</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9471</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5198</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6996</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>20248</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>593; 5012</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>526; 5215</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2919; 19458</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1225; 6665</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2354; 8942</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4174; 20505</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2603; 10233</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3605; 11492</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>10032; 33930</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3507</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4977</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9410</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5187</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8289</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12916</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9316</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>13266</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1317; 6950</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1362; 7710</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2268; 9085</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4979; 14187</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2253; 9553</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4546; 13088</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>8127; 18729</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5081; 14538</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>8601; 19278</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>17473</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21668</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>32743</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23475</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33516</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40948</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>46712</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>66259</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>11723; 24369</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15703; 29345</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19656; 49918</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>16546; 31573</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>18317; 33834</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>24660; 45555</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>32332; 51727</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>37240; 56783</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>46865; 85107</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A98-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 27,82</t>
+          <t>6,93; 27,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 40,17</t>
+          <t>10,86; 40,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,58; 41,32</t>
+          <t>13,26; 39,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 31,11</t>
+          <t>8,67; 32,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 35,76</t>
+          <t>6,96; 35,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,12; 41,4</t>
+          <t>8,52; 45,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,12; 25,2</t>
+          <t>9,28; 24,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,66; 32,66</t>
+          <t>12,56; 33,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,55; 35,82</t>
+          <t>14,28; 35,6</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 29,04</t>
+          <t>10,45; 29,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,98; 35,17</t>
+          <t>14,03; 34,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 51,29</t>
+          <t>9,51; 55,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 23,2</t>
+          <t>5,04; 21,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,08; 36,57</t>
+          <t>14,72; 36,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,14; 24,88</t>
+          <t>9,43; 24,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,98; 22,61</t>
+          <t>9,46; 22,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,83; 31,94</t>
+          <t>16,58; 31,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,43; 33,03</t>
+          <t>11,44; 35,68</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 15,2</t>
+          <t>0,0; 15,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 18,88</t>
+          <t>1,9; 18,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 25,25</t>
+          <t>4,01; 25,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 19,18</t>
+          <t>3,54; 20,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,47; 32,16</t>
+          <t>9,11; 33,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 36,02</t>
+          <t>6,76; 37,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 15,11</t>
+          <t>3,7; 14,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 20,74</t>
+          <t>6,38; 20,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,49; 25,32</t>
+          <t>7,73; 25,93</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 16,92</t>
+          <t>3,17; 18,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 23,52</t>
+          <t>4,88; 25,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 29,73</t>
+          <t>7,7; 29,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,88; 31,01</t>
+          <t>12,29; 33,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 31,69</t>
+          <t>7,37; 30,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,45; 38,71</t>
+          <t>13,68; 37,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,36; 21,57</t>
+          <t>9,3; 21,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,07; 23,1</t>
+          <t>8,99; 24,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,36; 29,95</t>
+          <t>13,36; 29,47</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,11; 16,85</t>
+          <t>8,16; 17,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,02</t>
+          <t>11,96; 23,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,06; 28,09</t>
+          <t>11,04; 27,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,71; 20,43</t>
+          <t>10,67; 20,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,86; 27,45</t>
+          <t>15,43; 27,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,53; 25,0</t>
+          <t>13,15; 25,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 17,29</t>
+          <t>10,55; 17,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,85; 22,65</t>
+          <t>15,13; 23,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,02; 23,65</t>
+          <t>13,77; 23,99</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2023; 8749</t>
+          <t>2178; 8661</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2606; 9785</t>
+          <t>2646; 9944</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3509; 10677</t>
+          <t>3426; 10287</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2938; 10489</t>
+          <t>2922; 10885</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1706; 8644</t>
+          <t>1682; 8477</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2523; 11453</t>
+          <t>2358; 12468</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6597; 16421</t>
+          <t>6047; 15873</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6145; 15853</t>
+          <t>6097; 16145</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7252; 19163</t>
+          <t>7638; 19045</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3776; 11366</t>
+          <t>4090; 11682</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5968; 15016</t>
+          <t>5989; 14634</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3952; 22692</t>
+          <t>4209; 24687</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2089; 9353</t>
+          <t>2031; 8656</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6204; 15046</t>
+          <t>6056; 14994</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5832; 15874</t>
+          <t>6020; 15330</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7926; 17967</t>
+          <t>7517; 17690</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14114; 26777</t>
+          <t>13906; 26624</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12352; 35692</t>
+          <t>12363; 38554</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>593; 5012</t>
+          <t>0; 4991</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>526; 5215</t>
+          <t>525; 5187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2919; 19458</t>
+          <t>3089; 19692</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1225; 6665</t>
+          <t>1230; 7174</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2354; 8942</t>
+          <t>2533; 9439</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4174; 20505</t>
+          <t>3850; 21109</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2603; 10233</t>
+          <t>2508; 9527</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3605; 11492</t>
+          <t>3536; 11404</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10032; 33930</t>
+          <t>10353; 34747</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1317; 6950</t>
+          <t>1303; 7714</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1362; 7710</t>
+          <t>1600; 8474</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2268; 9085</t>
+          <t>2353; 8930</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4979; 14187</t>
+          <t>5625; 15135</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2253; 9553</t>
+          <t>2223; 9259</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4546; 13088</t>
+          <t>4626; 12713</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8127; 18729</t>
+          <t>8076; 19077</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5081; 14538</t>
+          <t>5659; 15304</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8601; 19278</t>
+          <t>8598; 18971</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11723; 24369</t>
+          <t>11808; 24872</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15703; 29345</t>
+          <t>15240; 29441</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19656; 49918</t>
+          <t>19615; 49092</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16546; 31573</t>
+          <t>16488; 31501</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18317; 33834</t>
+          <t>19022; 33523</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24660; 45555</t>
+          <t>23963; 46435</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32332; 51727</t>
+          <t>31577; 51700</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37240; 56783</t>
+          <t>37927; 58056</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46865; 85107</t>
+          <t>49549; 86352</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A98-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP16A98-Habitat-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+          <t>Menores que consumieron otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17,76%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18,87%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21,9%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>15,44%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>23,51%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25,39%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17,76%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,87%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 27,54</t>
+          <t>8,67; 31,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,86; 40,82</t>
+          <t>8,77; 37,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,26; 39,81</t>
+          <t>9,23; 45,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,67; 32,28</t>
+          <t>6,44; 28,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 35,06</t>
+          <t>11,71; 42,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,52; 45,07</t>
+          <t>12,69; 39,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,28; 24,36</t>
+          <t>9,6; 24,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,56; 33,26</t>
+          <t>11,86; 32,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,28; 35,6</t>
+          <t>14,21; 34,88</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,84%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24,74%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13,9%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>18,43%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>23,26%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>23,57%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,45; 29,85</t>
+          <t>4,91; 22,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,03; 34,27</t>
+          <t>13,91; 36,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 55,8</t>
+          <t>7,75; 22,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 21,47</t>
+          <t>9,96; 30,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,72; 36,44</t>
+          <t>13,36; 35,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 24,02</t>
+          <t>6,69; 27,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 22,27</t>
+          <t>9,22; 22,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,58; 31,75</t>
+          <t>16,33; 32,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,44; 35,68</t>
+          <t>9,48; 21,84</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,39%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17,34%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>6,81%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13,98%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,14</t>
+          <t>3,47; 19,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 18,78</t>
+          <t>8,3; 31,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 25,55</t>
+          <t>7,57; 38,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 20,64</t>
+          <t>1,81; 15,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 33,95</t>
+          <t>1,92; 18,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 37,08</t>
+          <t>12,67; 31,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 14,07</t>
+          <t>3,6; 13,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 20,58</t>
+          <t>6,85; 21,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 25,93</t>
+          <t>12,33; 31,89</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20,57%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17,21%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25,3%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>8,54%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>12,59%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16,29%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 18,78</t>
+          <t>11,93; 31,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 25,84</t>
+          <t>7,46; 31,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,7; 29,22</t>
+          <t>15,01; 40,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,29; 33,08</t>
+          <t>3,16; 18,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 30,72</t>
+          <t>5,36; 25,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,68; 37,6</t>
+          <t>8,16; 30,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,3; 21,97</t>
+          <t>9,27; 22,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 24,32</t>
+          <t>8,44; 23,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,36; 29,47</t>
+          <t>13,72; 29,8</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15,19%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18,36%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>12,08%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18,42%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 17,2</t>
+          <t>10,93; 20,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,96; 23,1</t>
+          <t>14,75; 26,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 27,62</t>
+          <t>13,24; 25,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,67; 20,38</t>
+          <t>8,16; 16,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,43; 27,19</t>
+          <t>11,59; 22,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,15; 25,49</t>
+          <t>14,25; 24,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,55; 17,28</t>
+          <t>10,65; 17,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,13; 23,15</t>
+          <t>14,93; 22,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 23,99</t>
+          <t>15,03; 23,36</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos (tasa de respuesta: 99,14%)</t>
+          <t>Menores que consumieron otros medicamentos (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>5990</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4562</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5392</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>4857</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>5728</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6561</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5990</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4562</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12721</t>
+          <t>11879</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2178; 8661</t>
+          <t>2924; 10682</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2646; 9944</t>
+          <t>2119; 9045</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3426; 10287</t>
+          <t>2272; 11238</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2922; 10885</t>
+          <t>2025; 8820</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1682; 8477</t>
+          <t>2852; 10332</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2358; 12468</t>
+          <t>3339; 10465</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6047; 15873</t>
+          <t>6259; 16277</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6097; 16145</t>
+          <t>5756; 15981</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7638; 19045</t>
+          <t>7238; 17767</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4775</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>10180</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7849</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7213</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>9930</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10427</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4775</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10180</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20023</t>
+          <t>13361</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4090; 11682</t>
+          <t>1979; 9038</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5989; 14634</t>
+          <t>5725; 15070</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4209; 24687</t>
+          <t>4376; 12474</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2031; 8656</t>
+          <t>3897; 11769</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6056; 14994</t>
+          <t>5706; 15124</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6020; 15330</t>
+          <t>2416; 9868</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7517; 17690</t>
+          <t>7323; 17498</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13906; 26624</t>
+          <t>13694; 27049</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12363; 38554</t>
+          <t>8776; 20224</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9078</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1897</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1881</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>10778</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3300</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5115</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20248</t>
+          <t>19871</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4991</t>
+          <t>1208; 6682</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>525; 5187</t>
+          <t>2308; 8730</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3089; 19692</t>
+          <t>3963; 19898</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1230; 7174</t>
+          <t>598; 5144</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2533; 9439</t>
+          <t>529; 5054</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3850; 21109</t>
+          <t>6440; 15993</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2508; 9527</t>
+          <t>2437; 9400</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3536; 11404</t>
+          <t>3795; 11733</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10353; 34747</t>
+          <t>12725; 32905</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9410</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5187</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7974</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>3507</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>4129</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4977</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9410</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5187</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13266</t>
+          <t>12994</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1303; 7714</t>
+          <t>5457; 14575</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1600; 8474</t>
+          <t>2250; 9360</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2353; 8930</t>
+          <t>4732; 12646</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5625; 15135</t>
+          <t>1299; 7535</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2223; 9259</t>
+          <t>1759; 8205</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4626; 12713</t>
+          <t>2424; 9023</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8076; 19077</t>
+          <t>8045; 19422</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5659; 15304</t>
+          <t>5311; 14927</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8598; 18971</t>
+          <t>8401; 18248</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>23475</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>30293</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>17473</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>21668</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>32743</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>23475</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>25045</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33516</t>
+          <t>27812</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>58105</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11808; 24872</t>
+          <t>16896; 31398</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15240; 29441</t>
+          <t>18186; 33081</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19615; 49092</t>
+          <t>21832; 42758</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16488; 31501</t>
+          <t>11807; 24464</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19022; 33523</t>
+          <t>14773; 29092</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23963; 46435</t>
+          <t>20372; 35456</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31577; 51700</t>
+          <t>31850; 51779</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>37927; 58056</t>
+          <t>37429; 57146</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>49549; 86352</t>
+          <t>46288; 71920</t>
         </is>
       </c>
     </row>
